--- a/artfynd/A 40860-2025 artfynd.xlsx
+++ b/artfynd/A 40860-2025 artfynd.xlsx
@@ -1276,32 +1276,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128109174</v>
+        <v>128109166</v>
       </c>
       <c r="B8" t="n">
-        <v>80168</v>
+        <v>80132</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6464</v>
+        <v>6458</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1311,10 +1311,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>492344</v>
+        <v>492393</v>
       </c>
       <c r="R8" t="n">
-        <v>6950949</v>
+        <v>6950905</v>
       </c>
       <c r="S8" t="n">
         <v>15</v>
@@ -1373,32 +1373,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128109166</v>
+        <v>128109174</v>
       </c>
       <c r="B9" t="n">
-        <v>80132</v>
+        <v>80168</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6458</v>
+        <v>6464</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1408,10 +1408,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>492393</v>
+        <v>492344</v>
       </c>
       <c r="R9" t="n">
-        <v>6950905</v>
+        <v>6950949</v>
       </c>
       <c r="S9" t="n">
         <v>15</v>

--- a/artfynd/A 40860-2025 artfynd.xlsx
+++ b/artfynd/A 40860-2025 artfynd.xlsx
@@ -1276,32 +1276,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128109166</v>
+        <v>128109174</v>
       </c>
       <c r="B8" t="n">
-        <v>80132</v>
+        <v>80168</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6458</v>
+        <v>6464</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1311,10 +1311,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>492393</v>
+        <v>492344</v>
       </c>
       <c r="R8" t="n">
-        <v>6950905</v>
+        <v>6950949</v>
       </c>
       <c r="S8" t="n">
         <v>15</v>
@@ -1373,32 +1373,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128109174</v>
+        <v>128109166</v>
       </c>
       <c r="B9" t="n">
-        <v>80168</v>
+        <v>80132</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6464</v>
+        <v>6458</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1408,10 +1408,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>492344</v>
+        <v>492393</v>
       </c>
       <c r="R9" t="n">
-        <v>6950949</v>
+        <v>6950905</v>
       </c>
       <c r="S9" t="n">
         <v>15</v>

--- a/artfynd/A 40860-2025 artfynd.xlsx
+++ b/artfynd/A 40860-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128109163</v>
       </c>
       <c r="B2" t="n">
-        <v>80133</v>
+        <v>80136</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>128109175</v>
       </c>
       <c r="B3" t="n">
-        <v>80168</v>
+        <v>80171</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>128109158</v>
       </c>
       <c r="B4" t="n">
-        <v>80161</v>
+        <v>80164</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -969,7 +969,7 @@
         <v>128109176</v>
       </c>
       <c r="B5" t="n">
-        <v>79029</v>
+        <v>79032</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1066,7 +1066,7 @@
         <v>128109170</v>
       </c>
       <c r="B6" t="n">
-        <v>80132</v>
+        <v>80135</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1182,7 +1182,7 @@
         <v>128109168</v>
       </c>
       <c r="B7" t="n">
-        <v>80132</v>
+        <v>80135</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1279,7 +1279,7 @@
         <v>128109174</v>
       </c>
       <c r="B8" t="n">
-        <v>80168</v>
+        <v>80171</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1376,7 +1376,7 @@
         <v>128109166</v>
       </c>
       <c r="B9" t="n">
-        <v>80132</v>
+        <v>80135</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1473,7 +1473,7 @@
         <v>128109161</v>
       </c>
       <c r="B10" t="n">
-        <v>80133</v>
+        <v>80136</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1570,7 +1570,7 @@
         <v>128109157</v>
       </c>
       <c r="B11" t="n">
-        <v>80161</v>
+        <v>80164</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1667,7 +1667,7 @@
         <v>128109165</v>
       </c>
       <c r="B12" t="n">
-        <v>80132</v>
+        <v>80135</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1764,7 +1764,7 @@
         <v>128109155</v>
       </c>
       <c r="B13" t="n">
-        <v>80161</v>
+        <v>80164</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1861,7 +1861,7 @@
         <v>128109172</v>
       </c>
       <c r="B14" t="n">
-        <v>80132</v>
+        <v>80135</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1958,7 +1958,7 @@
         <v>128109169</v>
       </c>
       <c r="B15" t="n">
-        <v>80132</v>
+        <v>80135</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2055,7 +2055,7 @@
         <v>128109173</v>
       </c>
       <c r="B16" t="n">
-        <v>80168</v>
+        <v>80171</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2152,7 +2152,7 @@
         <v>128109156</v>
       </c>
       <c r="B17" t="n">
-        <v>80161</v>
+        <v>80164</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2249,7 +2249,7 @@
         <v>128109162</v>
       </c>
       <c r="B18" t="n">
-        <v>80133</v>
+        <v>80136</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2346,7 +2346,7 @@
         <v>128109167</v>
       </c>
       <c r="B19" t="n">
-        <v>80132</v>
+        <v>80135</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2443,7 +2443,7 @@
         <v>128109171</v>
       </c>
       <c r="B20" t="n">
-        <v>80132</v>
+        <v>80135</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>

--- a/artfynd/A 40860-2025 artfynd.xlsx
+++ b/artfynd/A 40860-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128109163</v>
       </c>
       <c r="B2" t="n">
-        <v>80136</v>
+        <v>80189</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>128109175</v>
       </c>
       <c r="B3" t="n">
-        <v>80171</v>
+        <v>80224</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>128109158</v>
       </c>
       <c r="B4" t="n">
-        <v>80164</v>
+        <v>80217</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -969,7 +969,7 @@
         <v>128109176</v>
       </c>
       <c r="B5" t="n">
-        <v>79032</v>
+        <v>79083</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1066,7 +1066,7 @@
         <v>128109170</v>
       </c>
       <c r="B6" t="n">
-        <v>80135</v>
+        <v>80188</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1182,7 +1182,7 @@
         <v>128109168</v>
       </c>
       <c r="B7" t="n">
-        <v>80135</v>
+        <v>80188</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1279,7 +1279,7 @@
         <v>128109174</v>
       </c>
       <c r="B8" t="n">
-        <v>80171</v>
+        <v>80224</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1376,7 +1376,7 @@
         <v>128109166</v>
       </c>
       <c r="B9" t="n">
-        <v>80135</v>
+        <v>80188</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1473,7 +1473,7 @@
         <v>128109161</v>
       </c>
       <c r="B10" t="n">
-        <v>80136</v>
+        <v>80189</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1570,7 +1570,7 @@
         <v>128109157</v>
       </c>
       <c r="B11" t="n">
-        <v>80164</v>
+        <v>80217</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1667,7 +1667,7 @@
         <v>128109165</v>
       </c>
       <c r="B12" t="n">
-        <v>80135</v>
+        <v>80188</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1764,7 +1764,7 @@
         <v>128109155</v>
       </c>
       <c r="B13" t="n">
-        <v>80164</v>
+        <v>80217</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1861,7 +1861,7 @@
         <v>128109172</v>
       </c>
       <c r="B14" t="n">
-        <v>80135</v>
+        <v>80188</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1958,7 +1958,7 @@
         <v>128109169</v>
       </c>
       <c r="B15" t="n">
-        <v>80135</v>
+        <v>80188</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2055,7 +2055,7 @@
         <v>128109173</v>
       </c>
       <c r="B16" t="n">
-        <v>80171</v>
+        <v>80224</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2152,7 +2152,7 @@
         <v>128109156</v>
       </c>
       <c r="B17" t="n">
-        <v>80164</v>
+        <v>80217</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2249,7 +2249,7 @@
         <v>128109162</v>
       </c>
       <c r="B18" t="n">
-        <v>80136</v>
+        <v>80189</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2346,7 +2346,7 @@
         <v>128109167</v>
       </c>
       <c r="B19" t="n">
-        <v>80135</v>
+        <v>80188</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2443,7 +2443,7 @@
         <v>128109171</v>
       </c>
       <c r="B20" t="n">
-        <v>80135</v>
+        <v>80188</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>

--- a/artfynd/A 40860-2025 artfynd.xlsx
+++ b/artfynd/A 40860-2025 artfynd.xlsx
@@ -1761,32 +1761,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128109155</v>
+        <v>128109172</v>
       </c>
       <c r="B13" t="n">
-        <v>80217</v>
+        <v>80188</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6462</v>
+        <v>6458</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1796,10 +1796,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>492405</v>
+        <v>492298</v>
       </c>
       <c r="R13" t="n">
-        <v>6950922</v>
+        <v>6950934</v>
       </c>
       <c r="S13" t="n">
         <v>15</v>
@@ -1858,32 +1858,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128109172</v>
+        <v>128109155</v>
       </c>
       <c r="B14" t="n">
-        <v>80188</v>
+        <v>80217</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6458</v>
+        <v>6462</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1893,10 +1893,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>492298</v>
+        <v>492405</v>
       </c>
       <c r="R14" t="n">
-        <v>6950934</v>
+        <v>6950922</v>
       </c>
       <c r="S14" t="n">
         <v>15</v>
@@ -1955,32 +1955,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128109169</v>
+        <v>128109173</v>
       </c>
       <c r="B15" t="n">
-        <v>80188</v>
+        <v>80224</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6458</v>
+        <v>6464</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -1990,10 +1990,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>492343</v>
+        <v>492369</v>
       </c>
       <c r="R15" t="n">
-        <v>6950951</v>
+        <v>6950895</v>
       </c>
       <c r="S15" t="n">
         <v>15</v>
@@ -2052,32 +2052,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128109173</v>
+        <v>128109169</v>
       </c>
       <c r="B16" t="n">
-        <v>80224</v>
+        <v>80188</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6464</v>
+        <v>6458</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2087,10 +2087,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>492369</v>
+        <v>492343</v>
       </c>
       <c r="R16" t="n">
-        <v>6950895</v>
+        <v>6950951</v>
       </c>
       <c r="S16" t="n">
         <v>15</v>

--- a/artfynd/A 40860-2025 artfynd.xlsx
+++ b/artfynd/A 40860-2025 artfynd.xlsx
@@ -1761,32 +1761,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128109172</v>
+        <v>128109155</v>
       </c>
       <c r="B13" t="n">
-        <v>80188</v>
+        <v>80217</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6458</v>
+        <v>6462</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1796,10 +1796,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>492298</v>
+        <v>492405</v>
       </c>
       <c r="R13" t="n">
-        <v>6950934</v>
+        <v>6950922</v>
       </c>
       <c r="S13" t="n">
         <v>15</v>
@@ -1858,32 +1858,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128109155</v>
+        <v>128109172</v>
       </c>
       <c r="B14" t="n">
-        <v>80217</v>
+        <v>80188</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6462</v>
+        <v>6458</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1893,10 +1893,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>492405</v>
+        <v>492298</v>
       </c>
       <c r="R14" t="n">
-        <v>6950922</v>
+        <v>6950934</v>
       </c>
       <c r="S14" t="n">
         <v>15</v>
@@ -1955,32 +1955,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128109173</v>
+        <v>128109169</v>
       </c>
       <c r="B15" t="n">
-        <v>80224</v>
+        <v>80188</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6464</v>
+        <v>6458</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -1990,10 +1990,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>492369</v>
+        <v>492343</v>
       </c>
       <c r="R15" t="n">
-        <v>6950895</v>
+        <v>6950951</v>
       </c>
       <c r="S15" t="n">
         <v>15</v>
@@ -2052,32 +2052,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128109169</v>
+        <v>128109173</v>
       </c>
       <c r="B16" t="n">
-        <v>80188</v>
+        <v>80224</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6458</v>
+        <v>6464</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2087,10 +2087,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>492343</v>
+        <v>492369</v>
       </c>
       <c r="R16" t="n">
-        <v>6950951</v>
+        <v>6950895</v>
       </c>
       <c r="S16" t="n">
         <v>15</v>

--- a/artfynd/A 40860-2025 artfynd.xlsx
+++ b/artfynd/A 40860-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY20"/>
+  <dimension ref="A1:AY23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -678,7 +678,7 @@
         <v>128109163</v>
       </c>
       <c r="B2" t="n">
-        <v>80189</v>
+        <v>80193</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>128109175</v>
       </c>
       <c r="B3" t="n">
-        <v>80224</v>
+        <v>80228</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>128109158</v>
       </c>
       <c r="B4" t="n">
-        <v>80217</v>
+        <v>80221</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -969,7 +969,7 @@
         <v>128109176</v>
       </c>
       <c r="B5" t="n">
-        <v>79083</v>
+        <v>79087</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1066,7 +1066,7 @@
         <v>128109170</v>
       </c>
       <c r="B6" t="n">
-        <v>80188</v>
+        <v>80192</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1182,7 +1182,7 @@
         <v>128109168</v>
       </c>
       <c r="B7" t="n">
-        <v>80188</v>
+        <v>80192</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1279,7 +1279,7 @@
         <v>128109174</v>
       </c>
       <c r="B8" t="n">
-        <v>80224</v>
+        <v>80228</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1376,7 +1376,7 @@
         <v>128109166</v>
       </c>
       <c r="B9" t="n">
-        <v>80188</v>
+        <v>80192</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1473,7 +1473,7 @@
         <v>128109161</v>
       </c>
       <c r="B10" t="n">
-        <v>80189</v>
+        <v>80193</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1570,7 +1570,7 @@
         <v>128109157</v>
       </c>
       <c r="B11" t="n">
-        <v>80217</v>
+        <v>80221</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1667,7 +1667,7 @@
         <v>128109165</v>
       </c>
       <c r="B12" t="n">
-        <v>80188</v>
+        <v>80192</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1764,7 +1764,7 @@
         <v>128109155</v>
       </c>
       <c r="B13" t="n">
-        <v>80217</v>
+        <v>80221</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1861,7 +1861,7 @@
         <v>128109172</v>
       </c>
       <c r="B14" t="n">
-        <v>80188</v>
+        <v>80192</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1958,7 +1958,7 @@
         <v>128109169</v>
       </c>
       <c r="B15" t="n">
-        <v>80188</v>
+        <v>80192</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2055,7 +2055,7 @@
         <v>128109173</v>
       </c>
       <c r="B16" t="n">
-        <v>80224</v>
+        <v>80228</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2152,7 +2152,7 @@
         <v>128109156</v>
       </c>
       <c r="B17" t="n">
-        <v>80217</v>
+        <v>80221</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2249,7 +2249,7 @@
         <v>128109162</v>
       </c>
       <c r="B18" t="n">
-        <v>80189</v>
+        <v>80193</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2346,7 +2346,7 @@
         <v>128109167</v>
       </c>
       <c r="B19" t="n">
-        <v>80188</v>
+        <v>80192</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2443,7 +2443,7 @@
         <v>128109171</v>
       </c>
       <c r="B20" t="n">
-        <v>80188</v>
+        <v>80192</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2534,6 +2534,325 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>128700678</v>
+      </c>
+      <c r="B21" t="n">
+        <v>90925</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>3286</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Flattoppad klubbsvamp</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Clavariadelphus truncatus</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>(Quél.) Donk</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr"/>
+      <c r="N21" t="inlineStr"/>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Fisktjärn, Jmt</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>492376</v>
+      </c>
+      <c r="R21" t="n">
+        <v>6950939</v>
+      </c>
+      <c r="S21" t="n">
+        <v>10</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Hackås</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2025-09-25</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2025-09-25</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF21" t="inlineStr"/>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Anders Wännström</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Anders Wännström</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>128700723</v>
+      </c>
+      <c r="B22" t="n">
+        <v>80192</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="J22" t="inlineStr"/>
+      <c r="K22" t="inlineStr"/>
+      <c r="N22" t="inlineStr"/>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Fisktjärn, Jmt</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>492335</v>
+      </c>
+      <c r="R22" t="n">
+        <v>6950936</v>
+      </c>
+      <c r="S22" t="n">
+        <v>10</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Hackås</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2025-09-25</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2025-09-25</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF22" t="inlineStr"/>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Anders Wännström</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Anders Wännström</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>128700788</v>
+      </c>
+      <c r="B23" t="n">
+        <v>57793</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>103031</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Lavskrika</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Perisoreus infaustus</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>förbiflygande</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr"/>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Fisktjärn, Jmt</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>492294</v>
+      </c>
+      <c r="R23" t="n">
+        <v>6950936</v>
+      </c>
+      <c r="S23" t="n">
+        <v>10</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Hackås</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2025-09-25</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2025-09-25</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Anders Wännström</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Anders Wännström</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 40860-2025 artfynd.xlsx
+++ b/artfynd/A 40860-2025 artfynd.xlsx
@@ -2540,7 +2540,7 @@
         <v>128700678</v>
       </c>
       <c r="B21" t="n">
-        <v>90925</v>
+        <v>90927</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2649,7 +2649,7 @@
         <v>128700723</v>
       </c>
       <c r="B22" t="n">
-        <v>80192</v>
+        <v>80194</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>

--- a/artfynd/A 40860-2025 artfynd.xlsx
+++ b/artfynd/A 40860-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128109163</v>
       </c>
       <c r="B2" t="n">
-        <v>80193</v>
+        <v>80195</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>128109175</v>
       </c>
       <c r="B3" t="n">
-        <v>80228</v>
+        <v>80230</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>128109158</v>
       </c>
       <c r="B4" t="n">
-        <v>80221</v>
+        <v>80223</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -969,7 +969,7 @@
         <v>128109176</v>
       </c>
       <c r="B5" t="n">
-        <v>79087</v>
+        <v>79089</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1066,7 +1066,7 @@
         <v>128109170</v>
       </c>
       <c r="B6" t="n">
-        <v>80192</v>
+        <v>80194</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1182,7 +1182,7 @@
         <v>128109168</v>
       </c>
       <c r="B7" t="n">
-        <v>80192</v>
+        <v>80194</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1279,7 +1279,7 @@
         <v>128109174</v>
       </c>
       <c r="B8" t="n">
-        <v>80228</v>
+        <v>80230</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1376,7 +1376,7 @@
         <v>128109166</v>
       </c>
       <c r="B9" t="n">
-        <v>80192</v>
+        <v>80194</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1473,7 +1473,7 @@
         <v>128109161</v>
       </c>
       <c r="B10" t="n">
-        <v>80193</v>
+        <v>80195</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1570,7 +1570,7 @@
         <v>128109157</v>
       </c>
       <c r="B11" t="n">
-        <v>80221</v>
+        <v>80223</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1667,7 +1667,7 @@
         <v>128109165</v>
       </c>
       <c r="B12" t="n">
-        <v>80192</v>
+        <v>80194</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1764,7 +1764,7 @@
         <v>128109155</v>
       </c>
       <c r="B13" t="n">
-        <v>80221</v>
+        <v>80223</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1861,7 +1861,7 @@
         <v>128109172</v>
       </c>
       <c r="B14" t="n">
-        <v>80192</v>
+        <v>80194</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1958,7 +1958,7 @@
         <v>128109169</v>
       </c>
       <c r="B15" t="n">
-        <v>80192</v>
+        <v>80194</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2055,7 +2055,7 @@
         <v>128109173</v>
       </c>
       <c r="B16" t="n">
-        <v>80228</v>
+        <v>80230</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2152,7 +2152,7 @@
         <v>128109156</v>
       </c>
       <c r="B17" t="n">
-        <v>80221</v>
+        <v>80223</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2249,7 +2249,7 @@
         <v>128109162</v>
       </c>
       <c r="B18" t="n">
-        <v>80193</v>
+        <v>80195</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2346,7 +2346,7 @@
         <v>128109167</v>
       </c>
       <c r="B19" t="n">
-        <v>80192</v>
+        <v>80194</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2443,7 +2443,7 @@
         <v>128109171</v>
       </c>
       <c r="B20" t="n">
-        <v>80192</v>
+        <v>80194</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>

--- a/artfynd/A 40860-2025 artfynd.xlsx
+++ b/artfynd/A 40860-2025 artfynd.xlsx
@@ -2540,7 +2540,7 @@
         <v>128700678</v>
       </c>
       <c r="B21" t="n">
-        <v>90927</v>
+        <v>90928</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>

--- a/artfynd/A 40860-2025 artfynd.xlsx
+++ b/artfynd/A 40860-2025 artfynd.xlsx
@@ -2540,7 +2540,7 @@
         <v>128700678</v>
       </c>
       <c r="B21" t="n">
-        <v>90928</v>
+        <v>90955</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2649,7 +2649,7 @@
         <v>128700723</v>
       </c>
       <c r="B22" t="n">
-        <v>80194</v>
+        <v>80221</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2750,7 +2750,7 @@
         <v>128700788</v>
       </c>
       <c r="B23" t="n">
-        <v>57793</v>
+        <v>57820</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>

--- a/artfynd/A 40860-2025 artfynd.xlsx
+++ b/artfynd/A 40860-2025 artfynd.xlsx
@@ -2540,7 +2540,7 @@
         <v>128700678</v>
       </c>
       <c r="B21" t="n">
-        <v>90955</v>
+        <v>90960</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2649,7 +2649,7 @@
         <v>128700723</v>
       </c>
       <c r="B22" t="n">
-        <v>80221</v>
+        <v>80225</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>

--- a/artfynd/A 40860-2025 artfynd.xlsx
+++ b/artfynd/A 40860-2025 artfynd.xlsx
@@ -2540,7 +2540,7 @@
         <v>128700678</v>
       </c>
       <c r="B21" t="n">
-        <v>90960</v>
+        <v>90965</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>

--- a/artfynd/A 40860-2025 artfynd.xlsx
+++ b/artfynd/A 40860-2025 artfynd.xlsx
@@ -2540,7 +2540,7 @@
         <v>128700678</v>
       </c>
       <c r="B21" t="n">
-        <v>90965</v>
+        <v>90969</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2649,7 +2649,7 @@
         <v>128700723</v>
       </c>
       <c r="B22" t="n">
-        <v>80225</v>
+        <v>80229</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2750,7 +2750,7 @@
         <v>128700788</v>
       </c>
       <c r="B23" t="n">
-        <v>57820</v>
+        <v>57824</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>

--- a/artfynd/A 40860-2025 artfynd.xlsx
+++ b/artfynd/A 40860-2025 artfynd.xlsx
@@ -2540,7 +2540,7 @@
         <v>128700678</v>
       </c>
       <c r="B21" t="n">
-        <v>90969</v>
+        <v>90974</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2649,7 +2649,7 @@
         <v>128700723</v>
       </c>
       <c r="B22" t="n">
-        <v>80229</v>
+        <v>80134</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2750,7 +2750,7 @@
         <v>128700788</v>
       </c>
       <c r="B23" t="n">
-        <v>57824</v>
+        <v>57827</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>

--- a/artfynd/A 40860-2025 artfynd.xlsx
+++ b/artfynd/A 40860-2025 artfynd.xlsx
@@ -2540,7 +2540,7 @@
         <v>128700678</v>
       </c>
       <c r="B21" t="n">
-        <v>90981</v>
+        <v>90984</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>

--- a/artfynd/A 40860-2025 artfynd.xlsx
+++ b/artfynd/A 40860-2025 artfynd.xlsx
@@ -2540,7 +2540,7 @@
         <v>128700678</v>
       </c>
       <c r="B21" t="n">
-        <v>90984</v>
+        <v>90987</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2649,7 +2649,7 @@
         <v>128700723</v>
       </c>
       <c r="B22" t="n">
-        <v>80139</v>
+        <v>80140</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>

--- a/artfynd/A 40860-2025 artfynd.xlsx
+++ b/artfynd/A 40860-2025 artfynd.xlsx
@@ -2540,7 +2540,7 @@
         <v>128700678</v>
       </c>
       <c r="B21" t="n">
-        <v>90987</v>
+        <v>90991</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2649,7 +2649,7 @@
         <v>128700723</v>
       </c>
       <c r="B22" t="n">
-        <v>80140</v>
+        <v>80144</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2750,7 +2750,7 @@
         <v>128700788</v>
       </c>
       <c r="B23" t="n">
-        <v>57827</v>
+        <v>57829</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>

--- a/artfynd/A 40860-2025 artfynd.xlsx
+++ b/artfynd/A 40860-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY23"/>
+  <dimension ref="A1:AY25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>128109163</v>
+        <v>128109161</v>
       </c>
       <c r="B2" t="n">
-        <v>80195</v>
+        <v>80433</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>492344</v>
+        <v>492368</v>
       </c>
       <c r="R2" t="n">
-        <v>6950948</v>
+        <v>6950897</v>
       </c>
       <c r="S2" t="n">
         <v>15</v>
@@ -772,32 +772,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128109175</v>
+        <v>128109162</v>
       </c>
       <c r="B3" t="n">
-        <v>80230</v>
+        <v>80433</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6464</v>
+        <v>2081</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -807,7 +807,7 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>492297</v>
+        <v>492335</v>
       </c>
       <c r="R3" t="n">
         <v>6950937</v>
@@ -869,32 +869,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128109158</v>
+        <v>128109163</v>
       </c>
       <c r="B4" t="n">
-        <v>80223</v>
+        <v>80433</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6462</v>
+        <v>2081</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -904,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>492326</v>
+        <v>492344</v>
       </c>
       <c r="R4" t="n">
-        <v>6950976</v>
+        <v>6950948</v>
       </c>
       <c r="S4" t="n">
         <v>15</v>
@@ -966,10 +966,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128109176</v>
+        <v>128700678</v>
       </c>
       <c r="B5" t="n">
-        <v>79089</v>
+        <v>91361</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -977,37 +977,48 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>3286</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Flattoppad klubbsvamp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Clavariadelphus truncatus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
+          <t>(Quél.) Donk</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Övre Fisktjärnen, Jmt</t>
+          <t>Fisktjärn, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>492299</v>
+        <v>492376</v>
       </c>
       <c r="R5" t="n">
-        <v>6950959</v>
+        <v>6950939</v>
       </c>
       <c r="S5" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1031,12 +1042,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-08-30</t>
+          <t>2025-09-25</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2025-08-30</t>
+          <t>2025-09-25</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1045,66 +1056,64 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Anders Wännström</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Anders Wännström</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128109170</v>
+        <v>128109176</v>
       </c>
       <c r="B6" t="n">
-        <v>80194</v>
+        <v>79327</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
-      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Övre Fisktjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>492334</v>
+        <v>492299</v>
       </c>
       <c r="R6" t="n">
-        <v>6950974</v>
+        <v>6950959</v>
       </c>
       <c r="S6" t="n">
         <v>15</v>
@@ -1145,24 +1154,8 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ6" t="inlineStr">
-        <is>
-          <t>björkar</t>
-        </is>
-      </c>
-      <c r="AK6" t="inlineStr">
-        <is>
-          <t>Betula</t>
-        </is>
-      </c>
-      <c r="AO6" t="inlineStr">
-        <is>
-          <t>Betula</t>
-        </is>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
@@ -1179,10 +1172,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128109168</v>
+        <v>128109165</v>
       </c>
       <c r="B7" t="n">
-        <v>80194</v>
+        <v>80432</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1214,10 +1207,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>492363</v>
+        <v>492371</v>
       </c>
       <c r="R7" t="n">
-        <v>6950933</v>
+        <v>6950899</v>
       </c>
       <c r="S7" t="n">
         <v>15</v>
@@ -1276,32 +1269,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128109174</v>
+        <v>128109166</v>
       </c>
       <c r="B8" t="n">
-        <v>80230</v>
+        <v>80432</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6464</v>
+        <v>6458</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1311,10 +1304,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>492344</v>
+        <v>492393</v>
       </c>
       <c r="R8" t="n">
-        <v>6950949</v>
+        <v>6950905</v>
       </c>
       <c r="S8" t="n">
         <v>15</v>
@@ -1373,10 +1366,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128109166</v>
+        <v>128109167</v>
       </c>
       <c r="B9" t="n">
-        <v>80194</v>
+        <v>80432</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1408,10 +1401,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>492393</v>
+        <v>492387</v>
       </c>
       <c r="R9" t="n">
-        <v>6950905</v>
+        <v>6950944</v>
       </c>
       <c r="S9" t="n">
         <v>15</v>
@@ -1470,10 +1463,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128109161</v>
+        <v>128109168</v>
       </c>
       <c r="B10" t="n">
-        <v>80195</v>
+        <v>80432</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1481,21 +1474,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>2081</v>
+        <v>6458</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1505,10 +1498,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>492368</v>
+        <v>492363</v>
       </c>
       <c r="R10" t="n">
-        <v>6950897</v>
+        <v>6950933</v>
       </c>
       <c r="S10" t="n">
         <v>15</v>
@@ -1567,32 +1560,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>128109157</v>
+        <v>128109169</v>
       </c>
       <c r="B11" t="n">
-        <v>80223</v>
+        <v>80432</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6462</v>
+        <v>6458</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1602,10 +1595,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>492359</v>
+        <v>492343</v>
       </c>
       <c r="R11" t="n">
-        <v>6950957</v>
+        <v>6950951</v>
       </c>
       <c r="S11" t="n">
         <v>15</v>
@@ -1664,10 +1657,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128109165</v>
+        <v>128109170</v>
       </c>
       <c r="B12" t="n">
-        <v>80194</v>
+        <v>80432</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1693,16 +1686,19 @@
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Övre Fisktjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>492371</v>
+        <v>492334</v>
       </c>
       <c r="R12" t="n">
-        <v>6950899</v>
+        <v>6950974</v>
       </c>
       <c r="S12" t="n">
         <v>15</v>
@@ -1743,8 +1739,24 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
+      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ12" t="inlineStr">
+        <is>
+          <t>björkar</t>
+        </is>
+      </c>
+      <c r="AK12" t="inlineStr">
+        <is>
+          <t>Betula</t>
+        </is>
+      </c>
+      <c r="AO12" t="inlineStr">
+        <is>
+          <t>Betula</t>
+        </is>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
@@ -1761,32 +1773,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128109155</v>
+        <v>128109171</v>
       </c>
       <c r="B13" t="n">
-        <v>80223</v>
+        <v>80432</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6462</v>
+        <v>6458</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1796,10 +1808,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>492405</v>
+        <v>492324</v>
       </c>
       <c r="R13" t="n">
-        <v>6950922</v>
+        <v>6950977</v>
       </c>
       <c r="S13" t="n">
         <v>15</v>
@@ -1861,7 +1873,7 @@
         <v>128109172</v>
       </c>
       <c r="B14" t="n">
-        <v>80194</v>
+        <v>80432</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1955,10 +1967,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128109169</v>
+        <v>128700723</v>
       </c>
       <c r="B15" t="n">
-        <v>80194</v>
+        <v>80432</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1984,19 +1996,22 @@
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
+      <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Övre Fisktjärnen, Jmt</t>
+          <t>Fisktjärn, Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>492343</v>
+        <v>492335</v>
       </c>
       <c r="R15" t="n">
-        <v>6950951</v>
+        <v>6950936</v>
       </c>
       <c r="S15" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2020,12 +2035,12 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2025-08-30</t>
+          <t>2025-09-25</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2025-08-30</t>
+          <t>2025-09-25</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2034,28 +2049,29 @@
       <c r="AE15" t="b">
         <v>0</v>
       </c>
+      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Anders Wännström</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Anders Wännström</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128109173</v>
+        <v>128109155</v>
       </c>
       <c r="B16" t="n">
-        <v>80230</v>
+        <v>80461</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2063,21 +2079,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6464</v>
+        <v>6462</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2087,10 +2103,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>492369</v>
+        <v>492405</v>
       </c>
       <c r="R16" t="n">
-        <v>6950895</v>
+        <v>6950922</v>
       </c>
       <c r="S16" t="n">
         <v>15</v>
@@ -2152,7 +2168,7 @@
         <v>128109156</v>
       </c>
       <c r="B17" t="n">
-        <v>80223</v>
+        <v>80461</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2246,32 +2262,32 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128109162</v>
+        <v>128109157</v>
       </c>
       <c r="B18" t="n">
-        <v>80195</v>
+        <v>80461</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>2081</v>
+        <v>6462</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2281,10 +2297,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>492335</v>
+        <v>492359</v>
       </c>
       <c r="R18" t="n">
-        <v>6950937</v>
+        <v>6950957</v>
       </c>
       <c r="S18" t="n">
         <v>15</v>
@@ -2343,32 +2359,32 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>128109167</v>
+        <v>128109158</v>
       </c>
       <c r="B19" t="n">
-        <v>80194</v>
+        <v>80461</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6458</v>
+        <v>6462</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2378,10 +2394,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>492387</v>
+        <v>492326</v>
       </c>
       <c r="R19" t="n">
-        <v>6950944</v>
+        <v>6950976</v>
       </c>
       <c r="S19" t="n">
         <v>15</v>
@@ -2440,32 +2456,32 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>128109171</v>
+        <v>128109173</v>
       </c>
       <c r="B20" t="n">
-        <v>80194</v>
+        <v>80468</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6458</v>
+        <v>6464</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2475,10 +2491,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>492324</v>
+        <v>492369</v>
       </c>
       <c r="R20" t="n">
-        <v>6950977</v>
+        <v>6950895</v>
       </c>
       <c r="S20" t="n">
         <v>15</v>
@@ -2537,59 +2553,48 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>128700678</v>
+        <v>128109174</v>
       </c>
       <c r="B21" t="n">
-        <v>90991</v>
+        <v>80468</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>3286</v>
+        <v>6464</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Flattoppad klubbsvamp</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Clavariadelphus truncatus</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Quél.) Donk</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K21" t="inlineStr"/>
-      <c r="N21" t="inlineStr"/>
+          <t>(L.) Ach.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Fisktjärn, Jmt</t>
+          <t>Övre Fisktjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>492376</v>
+        <v>492344</v>
       </c>
       <c r="R21" t="n">
-        <v>6950939</v>
+        <v>6950949</v>
       </c>
       <c r="S21" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2613,12 +2618,12 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2025-09-25</t>
+          <t>2025-08-30</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2025-09-25</t>
+          <t>2025-08-30</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2627,70 +2632,66 @@
       <c r="AE21" t="b">
         <v>0</v>
       </c>
-      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
       </c>
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Anders Wännström</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Anders Wännström</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>128700723</v>
+        <v>128109175</v>
       </c>
       <c r="B22" t="n">
-        <v>80144</v>
+        <v>80468</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6458</v>
+        <v>6464</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="J22" t="inlineStr"/>
-      <c r="K22" t="inlineStr"/>
-      <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Fisktjärn, Jmt</t>
+          <t>Övre Fisktjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>492335</v>
+        <v>492297</v>
       </c>
       <c r="R22" t="n">
-        <v>6950936</v>
+        <v>6950937</v>
       </c>
       <c r="S22" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2714,12 +2715,12 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2025-09-25</t>
+          <t>2025-08-30</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2025-09-25</t>
+          <t>2025-08-30</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2728,19 +2729,18 @@
       <c r="AE22" t="b">
         <v>0</v>
       </c>
-      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
       </c>
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Anders Wännström</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Anders Wännström</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
@@ -2750,11 +2750,11 @@
         <v>128700788</v>
       </c>
       <c r="B23" t="n">
-        <v>57829</v>
+        <v>58057</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
@@ -2853,6 +2853,225 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>134422503</v>
+      </c>
+      <c r="B24" t="n">
+        <v>58596</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>103041</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Bergfink</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Fringilla montifringilla</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Övre Fisktjärnen, Övre Fisktjärnen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>492255</v>
+      </c>
+      <c r="R24" t="n">
+        <v>6950953</v>
+      </c>
+      <c r="S24" t="n">
+        <v>20</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Hackås</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="Z24" t="inlineStr">
+        <is>
+          <t>21:02</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="AB24" t="inlineStr">
+        <is>
+          <t>21:02</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Erik Wilhelmsson</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Erik Wilhelmsson</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>134423290</v>
+      </c>
+      <c r="B25" t="n">
+        <v>99001</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>223049</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Ormbär</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Paris quadrifolia</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Övre Fisktjärnen, Övre Fisktjärnen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>492296</v>
+      </c>
+      <c r="R25" t="n">
+        <v>6950946</v>
+      </c>
+      <c r="S25" t="n">
+        <v>10</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Hackås</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="Z25" t="inlineStr">
+        <is>
+          <t>21:31</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="AB25" t="inlineStr">
+        <is>
+          <t>21:31</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Erik Wilhelmsson</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Erik Wilhelmsson</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 40860-2025 artfynd.xlsx
+++ b/artfynd/A 40860-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY25"/>
+  <dimension ref="A1:AZ25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128109161</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -866,6 +876,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128109162</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -963,6 +978,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128109163</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1072,6 +1092,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128700678</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1169,6 +1194,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128109176</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1266,6 +1296,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128109165</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1363,6 +1398,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128109166</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1460,6 +1500,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128109167</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1557,6 +1602,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128109168</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1654,6 +1704,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128109169</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1770,6 +1825,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128109170</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1867,6 +1927,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128109171</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1964,6 +2029,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128109172</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2065,6 +2135,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128700723</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2162,6 +2237,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128109155</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2259,6 +2339,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128109156</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2356,6 +2441,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128109157</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2453,6 +2543,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128109158</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2550,6 +2645,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128109173</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2647,6 +2747,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128109174</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2744,6 +2849,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128109175</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2853,6 +2963,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128700788</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -2965,6 +3080,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134422503</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3072,8 +3192,39 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134423290</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>